--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488068_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488068_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.224299999999999</v>
+        <v>10.0696</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9956</v>
+        <v>8.3636</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2286</v>
+        <v>1.706</v>
       </c>
       <c r="G2" t="n">
         <v>6.8921</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.203</v>
+        <v>0.6423</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.4342</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2692</v>
+        <v>0.2081</v>
       </c>
       <c r="V2" t="n">
         <v>1.5441</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>G. CARRAL ESCUDERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5093</v>
+        <v>5.9608</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9607</v>
+        <v>2.8649</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5486</v>
+        <v>3.096</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2233</v>
+        <v>3.4495</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0405</v>
+        <v>0.7824</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1828</v>
+        <v>2.667</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5598</v>
+        <v>3.145</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3417</v>
+        <v>0.7668</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2181</v>
+        <v>2.3783</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3365</v>
+        <v>0.3045</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6988</v>
+        <v>0.0157</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0353</v>
+        <v>0.2888</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.1716</v>
+        <v>1.1893</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.9467</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7751</v>
+        <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9839</v>
+        <v>-0.3478</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6668</v>
+        <v>-0.9589</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3171</v>
+        <v>0.611</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4737</v>
+        <v>1.6698</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6808</v>
+        <v>1.6698</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. CARRAL ESCUDERO</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6281</v>
+        <v>5.1423</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7006</v>
+        <v>2.9025</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9275</v>
+        <v>2.2397</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4495</v>
+        <v>5.2233</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7824</v>
+        <v>3.0405</v>
       </c>
       <c r="I4" t="n">
-        <v>2.667</v>
+        <v>2.1828</v>
       </c>
       <c r="J4" t="n">
-        <v>3.145</v>
+        <v>5.5598</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7668</v>
+        <v>2.3417</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3783</v>
+        <v>3.2181</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3045</v>
+        <v>-0.3365</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0157</v>
+        <v>0.6988</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2888</v>
+        <v>-1.0353</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1893</v>
+        <v>-3.1716</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>-5.9467</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1805</v>
+        <v>2.7751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6806</v>
+        <v>1.6169</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1232</v>
+        <v>0.6086</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4426</v>
+        <v>1.0083</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6698</v>
+        <v>1.4737</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6698</v>
+        <v>2.6808</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. DAVID ROCHA</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5664</v>
+        <v>2.6981</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0631</v>
+        <v>-1.3027</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6295</v>
+        <v>4.0008</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2466</v>
+        <v>2.5645</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1653</v>
+        <v>1.9046</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4119</v>
+        <v>0.6599</v>
       </c>
       <c r="J5" t="n">
-        <v>1.274</v>
+        <v>3.3973</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0207</v>
+        <v>2.63</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2533</v>
+        <v>0.7673</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0274</v>
+        <v>-0.8328</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1861</v>
+        <v>-0.7255</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1586</v>
+        <v>-0.1073</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9645</v>
+        <v>-2.9733</v>
       </c>
       <c r="R5" t="n">
         <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2952</v>
+        <v>0.1138</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6205000000000001</v>
+        <v>-0.7157</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6747</v>
+        <v>0.8294</v>
       </c>
       <c r="V5" t="n">
-        <v>2.0068</v>
+        <v>1.0109</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0068</v>
+        <v>-1.0109</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.0219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ VILLEGAS</t>
+          <t>D. DAVID ROCHA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2217</v>
+        <v>2.4632</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9262</v>
+        <v>-0.4082</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2955</v>
+        <v>2.8714</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1715</v>
+        <v>1.2466</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6225000000000001</v>
+        <v>-0.1653</v>
       </c>
       <c r="I6" t="n">
-        <v>0.549</v>
+        <v>1.4119</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5501</v>
+        <v>1.274</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7466</v>
+        <v>0.0207</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8036</v>
+        <v>1.2533</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3786</v>
+        <v>-0.0274</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1241</v>
+        <v>-0.1861</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2545</v>
+        <v>0.1586</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9911</v>
+        <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0591</v>
+        <v>1.192</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.624</v>
+        <v>0.2754</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.9166</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.0068</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.0068</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>A. RODRIGUEZ VILLEGAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9412</v>
+        <v>2.414</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.835</v>
+        <v>1.0904</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7761</v>
+        <v>1.3236</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5645</v>
+        <v>1.1715</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9046</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6599</v>
+        <v>0.549</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3973</v>
+        <v>1.5501</v>
       </c>
       <c r="K7" t="n">
-        <v>2.63</v>
+        <v>0.7466</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7673</v>
+        <v>0.8036</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8328</v>
+        <v>-0.3786</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7255</v>
+        <v>-0.1241</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1073</v>
+        <v>-0.2545</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9911</v>
+        <v>0.9911</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9822</v>
+        <v>0.9911</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6431</v>
+        <v>0.2514</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2479</v>
+        <v>-0.4597</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6048</v>
+        <v>0.7111</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0109</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.0109</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.0219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7308</v>
+        <v>1.1582</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2826</v>
+        <v>-2.2202</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0134</v>
+        <v>3.3784</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0329</v>
@@ -1078,13 +1078,13 @@
         <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1075</v>
+        <v>0.5349</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0696</v>
+        <v>-0.0072</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1772</v>
+        <v>0.5422</v>
       </c>
       <c r="V8" t="n">
         <v>0.674</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4546</v>
+        <v>0.9973</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5851</v>
+        <v>-0.1547</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0397</v>
+        <v>1.152</v>
       </c>
       <c r="G9" t="n">
         <v>0.679</v>
@@ -1156,13 +1156,13 @@
         <v>1.9822</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.707</v>
+        <v>-0.1643</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6864</v>
+        <v>-0.256</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0206</v>
+        <v>0.0917</v>
       </c>
       <c r="V9" t="n">
         <v>1.4737</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>D. VILLEGAS GIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1527</v>
+        <v>0.1827</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9122</v>
+        <v>0.8072</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0649</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0418</v>
+        <v>-0.0678</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4754</v>
+        <v>0.5999</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5172</v>
+        <v>-0.6677</v>
       </c>
       <c r="J10" t="n">
-        <v>0.663</v>
+        <v>0.6659</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2579</v>
+        <v>0.6659</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5949</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7048</v>
+        <v>-0.7337</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2175</v>
+        <v>-0.066</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9223</v>
+        <v>-0.6677</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5909</v>
+        <v>0.0523</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8001</v>
+        <v>0.1413</v>
       </c>
       <c r="U10" t="n">
-        <v>1.391</v>
+        <v>-0.089</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. VILLEGAS GIMENEZ</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0491</v>
+        <v>-0.2052</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6035</v>
+        <v>-0.7085</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6526</v>
+        <v>0.5033</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0678</v>
+        <v>-0.0418</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5999</v>
+        <v>1.4754</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6677</v>
+        <v>-1.5172</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6659</v>
+        <v>0.663</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6659</v>
+        <v>1.2579</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.5949</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7337</v>
+        <v>-0.7048</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.066</v>
+        <v>0.2175</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6677</v>
+        <v>-0.9223</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1795</v>
+        <v>0.233</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0624</v>
+        <v>-0.5964</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1171</v>
+        <v>0.8294</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4672</v>
+        <v>-3.3445</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5447</v>
+        <v>-1.6465</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9226</v>
+        <v>-1.6979</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4943</v>
@@ -1390,13 +1390,13 @@
         <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4324</v>
+        <v>0.5552</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6278</v>
+        <v>0.5259</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1953</v>
+        <v>0.0293</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6036</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>26.9128</v>
+        <v>27.5365</v>
       </c>
       <c r="E13" t="n">
-        <v>8.963899999999997</v>
+        <v>9.5878</v>
       </c>
       <c r="F13" t="n">
-        <v>17.9486</v>
+        <v>17.9488</v>
       </c>
       <c r="G13" t="n">
-        <v>15.58970000000001</v>
+        <v>15.5897</v>
       </c>
       <c r="H13" t="n">
         <v>10.8072</v>
       </c>
       <c r="I13" t="n">
-        <v>4.782300000000001</v>
+        <v>4.782299999999999</v>
       </c>
       <c r="J13" t="n">
         <v>20.5805</v>
@@ -1450,10 +1450,10 @@
         <v>9.2514</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.990900000000001</v>
+        <v>-4.9909</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5222000000000002</v>
+        <v>-0.5222000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-4.4687</v>
@@ -1468,13 +1468,13 @@
         <v>17.8399</v>
       </c>
       <c r="S13" t="n">
-        <v>4.055800000000001</v>
+        <v>4.6797</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6323</v>
+        <v>-1.0085</v>
       </c>
       <c r="U13" t="n">
-        <v>5.688200000000001</v>
+        <v>5.688099999999999</v>
       </c>
       <c r="V13" t="n">
         <v>9.2494</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4696</v>
+        <v>0.3854</v>
       </c>
       <c r="E15" t="n">
         <v>0.7344000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2648</v>
+        <v>-0.3491</v>
       </c>
       <c r="G15" t="n">
         <v>1.4591</v>
@@ -1624,13 +1624,13 @@
         <v>2.7751</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0283</v>
+        <v>-0.0559</v>
       </c>
       <c r="T15" t="n">
         <v>-0.9211</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9494</v>
+        <v>0.8652</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8107</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>J. MOLINA VERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2034</v>
+        <v>-0.4018</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3832</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1799</v>
+        <v>-0.4018</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2005</v>
+        <v>-0.4018</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.5015</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.301</v>
+        <v>-0.4018</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3646</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2896</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1255</v>
+        <v>-0.4018</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1369</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0114</v>
+        <v>-0.4018</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4797</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6829</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7968</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MOLINA VERA</t>
+          <t>A. GARCIA GUERRERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4018</v>
+        <v>-1.1988</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-1.0133</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4018</v>
+        <v>-0.1854</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4018</v>
+        <v>-1.0368</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0.9469</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4018</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.639</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0.6791</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4018</v>
+        <v>-0.3979</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.2677</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4018</v>
+        <v>-0.1301</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.0936</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.3744</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.2808</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARCIA GUERRERO</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3672</v>
+        <v>-1.271</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0133</v>
+        <v>-1.1982</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3539</v>
+        <v>-0.0728</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0368</v>
+        <v>-1.2005</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9469</v>
+        <v>-2.5015</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.08989999999999999</v>
+        <v>1.301</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.639</v>
+        <v>-0.075</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6791</v>
+        <v>-1.3646</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>1.2896</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3979</v>
+        <v>-1.1255</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2677</v>
+        <v>-1.1369</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1301</v>
+        <v>0.0114</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1982</v>
+        <v>1.9822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2621</v>
+        <v>0.412</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3744</v>
+        <v>-0.132</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1123</v>
+        <v>0.5441</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2666</v>
+        <v>-1.4737</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2666</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5272</v>
+        <v>-1.539</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6926</v>
+        <v>-0.8963</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8346</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4302</v>
@@ -1936,13 +1936,13 @@
         <v>1.9822</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0595</v>
+        <v>0.0477</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1944</v>
+        <v>-0.3982</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2539</v>
+        <v>0.4459</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1476</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6358</v>
+        <v>-1.8783</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0384</v>
+        <v>-2.529</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4026</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7973</v>
@@ -2014,13 +2014,13 @@
         <v>2.7751</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.019</v>
+        <v>-0.2615</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3103</v>
+        <v>-0.801</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2914</v>
+        <v>0.5395</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6036</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0371</v>
+        <v>-2.1777</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6942</v>
+        <v>-0.0829</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3429</v>
+        <v>-2.0948</v>
       </c>
       <c r="G21" t="n">
         <v>0.42</v>
@@ -2092,13 +2092,13 @@
         <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.0101</v>
+        <v>-1.1507</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4755</v>
+        <v>-0.8643</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5346</v>
+        <v>-0.2865</v>
       </c>
       <c r="V21" t="n">
         <v>0.337</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7854</v>
+        <v>-4.7068</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6409</v>
+        <v>-2.5578</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1445</v>
+        <v>-2.1491</v>
       </c>
       <c r="G22" t="n">
         <v>-5.663</v>
@@ -2170,13 +2170,13 @@
         <v>2.1805</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5673</v>
+        <v>-0.3541</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3637</v>
+        <v>-0.5531</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2036</v>
+        <v>0.199</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8701</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.4448</v>
+        <v>-7.3605</v>
       </c>
       <c r="E23" t="n">
         <v>-5.4867</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9581</v>
+        <v>-1.8739</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9732</v>
@@ -2248,13 +2248,13 @@
         <v>2.1805</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2139</v>
+        <v>-1.1296</v>
       </c>
       <c r="T23" t="n">
         <v>-0.7963</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4175</v>
+        <v>-0.3333</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4737</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.4903</v>
+        <v>-7.5957</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.2445</v>
+        <v>-6.4296</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2457</v>
+        <v>-1.1661</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4766</v>
@@ -2326,13 +2326,13 @@
         <v>3.568</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6856</v>
+        <v>-0.791</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6627</v>
+        <v>-0.8477</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.023</v>
+        <v>0.0567</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9405</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-26.9127</v>
+        <v>-26.2335</v>
       </c>
       <c r="E25" t="n">
         <v>-17.9487</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.963799999999999</v>
+        <v>-8.284899999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-15.5896</v>
@@ -2404,16 +2404,16 @@
         <v>19.8223</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.055899999999999</v>
+        <v>-3.3767</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.688099999999999</v>
+        <v>-5.6881</v>
       </c>
       <c r="U25" t="n">
-        <v>1.6323</v>
+        <v>2.3114</v>
       </c>
       <c r="V25" t="n">
-        <v>-9.249499999999999</v>
+        <v>-9.249500000000001</v>
       </c>
       <c r="W25" t="n">
         <v>0.5883999999999997</v>
